--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R361"/>
+  <dimension ref="A1:R363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21969,11 +21969,131 @@
         <v>386.16</v>
       </c>
       <c r="Q361" t="n">
-        <v>342.6</v>
+        <v>354.2</v>
       </c>
       <c r="R361" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>410.78</v>
+      </c>
+      <c r="C362" t="n">
+        <v>403.68</v>
+      </c>
+      <c r="D362" t="n">
+        <v>390.35</v>
+      </c>
+      <c r="E362" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="F362" t="n">
+        <v>367.85</v>
+      </c>
+      <c r="G362" t="n">
+        <v>345.77</v>
+      </c>
+      <c r="H362" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="I362" t="n">
+        <v>370.31</v>
+      </c>
+      <c r="J362" t="n">
+        <v>363.35</v>
+      </c>
+      <c r="K362" t="n">
+        <v>374.52</v>
+      </c>
+      <c r="L362" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="M362" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="N362" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="O362" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="P362" t="n">
+        <v>385.65</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>408.26</v>
+      </c>
+      <c r="C363" t="n">
+        <v>404.94</v>
+      </c>
+      <c r="D363" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="E363" t="n">
+        <v>376.01</v>
+      </c>
+      <c r="F363" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="G363" t="n">
+        <v>344.09</v>
+      </c>
+      <c r="H363" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="I363" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="J363" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="K363" t="n">
+        <v>370.99</v>
+      </c>
+      <c r="L363" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="M363" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="N363" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="O363" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="P363" t="n">
+        <v>383.67</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21988,7 +22108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25761,6 +25881,26 @@
       </c>
       <c r="B377" t="n">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -25929,28 +26069,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.349299374541973</v>
+        <v>-0.329108023516051</v>
       </c>
       <c r="J2" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03556484085840617</v>
+        <v>0.03166463298185496</v>
       </c>
       <c r="M2" t="n">
-        <v>11.31938081920136</v>
+        <v>11.37371990887352</v>
       </c>
       <c r="N2" t="n">
-        <v>192.5141160785112</v>
+        <v>193.6890671589713</v>
       </c>
       <c r="O2" t="n">
-        <v>13.87494562434431</v>
+        <v>13.91722196269684</v>
       </c>
       <c r="P2" t="n">
-        <v>398.5482542346674</v>
+        <v>398.3392740753792</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26007,28 +26147,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.00678823665405422</v>
+        <v>0.007845401081000875</v>
       </c>
       <c r="J3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>1.108799591253984e-05</v>
+        <v>1.489646869801131e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>12.56960368777779</v>
+        <v>12.58551054219748</v>
       </c>
       <c r="N3" t="n">
-        <v>240.6382967439042</v>
+        <v>240.4521924583515</v>
       </c>
       <c r="O3" t="n">
-        <v>15.5125206444312</v>
+        <v>15.50652096565672</v>
       </c>
       <c r="P3" t="n">
-        <v>389.9840525692028</v>
+        <v>389.8320608482371</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26085,28 +26225,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2417374317448821</v>
+        <v>-0.2344222363345484</v>
       </c>
       <c r="J4" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02972804862991019</v>
+        <v>0.02822619218347722</v>
       </c>
       <c r="M4" t="n">
-        <v>8.52169631477255</v>
+        <v>8.519090335763797</v>
       </c>
       <c r="N4" t="n">
-        <v>108.6735264154394</v>
+        <v>108.3440567990368</v>
       </c>
       <c r="O4" t="n">
-        <v>10.42465953474929</v>
+        <v>10.40884512321309</v>
       </c>
       <c r="P4" t="n">
-        <v>389.0351545380615</v>
+        <v>388.9581929695274</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26163,28 +26303,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6883686534141408</v>
+        <v>-0.6838051322404923</v>
       </c>
       <c r="J5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1847487757266412</v>
+        <v>0.1842184582773043</v>
       </c>
       <c r="M5" t="n">
-        <v>8.858144281615141</v>
+        <v>8.835926229471955</v>
       </c>
       <c r="N5" t="n">
-        <v>119.2642411191443</v>
+        <v>118.707485824006</v>
       </c>
       <c r="O5" t="n">
-        <v>10.92081687050673</v>
+        <v>10.8952965000502</v>
       </c>
       <c r="P5" t="n">
-        <v>390.401251304264</v>
+        <v>390.3533944522607</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26241,28 +26381,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4857386693748483</v>
+        <v>-0.4831189449299491</v>
       </c>
       <c r="J6" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09519581728488968</v>
+        <v>0.09516606691309171</v>
       </c>
       <c r="M6" t="n">
-        <v>8.74303791791883</v>
+        <v>8.708778294282078</v>
       </c>
       <c r="N6" t="n">
-        <v>127.7286009992648</v>
+        <v>127.0513819958424</v>
       </c>
       <c r="O6" t="n">
-        <v>11.30170787975272</v>
+        <v>11.27170714647264</v>
       </c>
       <c r="P6" t="n">
-        <v>378.0513233649255</v>
+        <v>378.0238710116679</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26319,28 +26459,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2314667045875853</v>
+        <v>-0.2390937010506315</v>
       </c>
       <c r="J7" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02392309940826021</v>
+        <v>0.02568622623038486</v>
       </c>
       <c r="M7" t="n">
-        <v>8.271995399949056</v>
+        <v>8.257523304557528</v>
       </c>
       <c r="N7" t="n">
-        <v>126.659506052083</v>
+        <v>126.2787698993694</v>
       </c>
       <c r="O7" t="n">
-        <v>11.25431055427577</v>
+        <v>11.23738269791366</v>
       </c>
       <c r="P7" t="n">
-        <v>358.6698988711087</v>
+        <v>358.7488618287774</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26397,28 +26537,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1508355914645789</v>
+        <v>-0.1485279101950249</v>
       </c>
       <c r="J8" t="n">
+        <v>362</v>
+      </c>
+      <c r="K8" t="n">
         <v>360</v>
       </c>
-      <c r="K8" t="n">
-        <v>358</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.009971340277918239</v>
+        <v>0.009771749323099432</v>
       </c>
       <c r="M8" t="n">
-        <v>8.806975056392377</v>
+        <v>8.772293643956877</v>
       </c>
       <c r="N8" t="n">
-        <v>129.7095315993128</v>
+        <v>129.0209027982641</v>
       </c>
       <c r="O8" t="n">
-        <v>11.38900924572953</v>
+        <v>11.35873684871096</v>
       </c>
       <c r="P8" t="n">
-        <v>369.3550574055385</v>
+        <v>369.3310092144878</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26475,28 +26615,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.39578880501047</v>
+        <v>-0.3927531348151687</v>
       </c>
       <c r="J9" t="n">
+        <v>362</v>
+      </c>
+      <c r="K9" t="n">
         <v>360</v>
       </c>
-      <c r="K9" t="n">
-        <v>358</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09655943582954352</v>
+        <v>0.09607721666076974</v>
       </c>
       <c r="M9" t="n">
-        <v>7.318653225740895</v>
+        <v>7.296203148649836</v>
       </c>
       <c r="N9" t="n">
-        <v>84.15925425719968</v>
+        <v>83.75894151923042</v>
       </c>
       <c r="O9" t="n">
-        <v>9.173835307939623</v>
+        <v>9.151991123205399</v>
       </c>
       <c r="P9" t="n">
-        <v>375.9591850861852</v>
+        <v>375.9275550248054</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26553,28 +26693,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0563503973721207</v>
+        <v>0.05773912571562251</v>
       </c>
       <c r="J10" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009192234010217959</v>
+        <v>0.0009751820650281129</v>
       </c>
       <c r="M10" t="n">
-        <v>10.922449626148</v>
+        <v>10.87357388665218</v>
       </c>
       <c r="N10" t="n">
-        <v>199.9712859915581</v>
+        <v>198.8962125237465</v>
       </c>
       <c r="O10" t="n">
-        <v>14.14112039378628</v>
+        <v>14.10305685033378</v>
       </c>
       <c r="P10" t="n">
-        <v>358.4718968212092</v>
+        <v>358.4575316452422</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26631,28 +26771,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1207477021914227</v>
+        <v>-0.1068141472197908</v>
       </c>
       <c r="J11" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001218647762901925</v>
+        <v>0.0009626067422523477</v>
       </c>
       <c r="M11" t="n">
-        <v>17.43151223588463</v>
+        <v>17.39430226558795</v>
       </c>
       <c r="N11" t="n">
-        <v>676.5248851766178</v>
+        <v>673.7608103992837</v>
       </c>
       <c r="O11" t="n">
-        <v>26.01009198708489</v>
+        <v>25.9569029431341</v>
       </c>
       <c r="P11" t="n">
-        <v>362.3152623553352</v>
+        <v>362.1680282026985</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26709,28 +26849,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4796310159224637</v>
+        <v>-0.4669847394762308</v>
       </c>
       <c r="J12" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K12" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06795886794313055</v>
+        <v>0.06499740209077498</v>
       </c>
       <c r="M12" t="n">
-        <v>10.82970949297655</v>
+        <v>10.8318844867985</v>
       </c>
       <c r="N12" t="n">
-        <v>179.5530186407682</v>
+        <v>179.4294797156523</v>
       </c>
       <c r="O12" t="n">
-        <v>13.39973949898908</v>
+        <v>13.39512895479742</v>
       </c>
       <c r="P12" t="n">
-        <v>372.5727174706768</v>
+        <v>372.4396293757704</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26787,28 +26927,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03187955545167868</v>
+        <v>-0.02552702369352269</v>
       </c>
       <c r="J13" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K13" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000536423862662172</v>
+        <v>0.0003469922739920417</v>
       </c>
       <c r="M13" t="n">
-        <v>8.087674090499139</v>
+        <v>8.077762381600664</v>
       </c>
       <c r="N13" t="n">
-        <v>109.850871657803</v>
+        <v>109.4602905293052</v>
       </c>
       <c r="O13" t="n">
-        <v>10.48097665572264</v>
+        <v>10.46232720427464</v>
       </c>
       <c r="P13" t="n">
-        <v>372.0227839497549</v>
+        <v>371.9570539870215</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26865,28 +27005,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3675746605549332</v>
+        <v>-0.3603661966001701</v>
       </c>
       <c r="J14" t="n">
+        <v>362</v>
+      </c>
+      <c r="K14" t="n">
         <v>360</v>
       </c>
-      <c r="K14" t="n">
-        <v>358</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.05107879794347803</v>
+        <v>0.04959918020376475</v>
       </c>
       <c r="M14" t="n">
-        <v>9.472354832118279</v>
+        <v>9.460058552222433</v>
       </c>
       <c r="N14" t="n">
-        <v>145.5480698754512</v>
+        <v>145.0326904252957</v>
       </c>
       <c r="O14" t="n">
-        <v>12.06433047771202</v>
+        <v>12.04295189832193</v>
       </c>
       <c r="P14" t="n">
-        <v>373.8452765900877</v>
+        <v>373.7707525198559</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26943,28 +27083,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2892979878144412</v>
+        <v>-0.2775314567087797</v>
       </c>
       <c r="J15" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K15" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02638949998230689</v>
+        <v>0.02448628156264165</v>
       </c>
       <c r="M15" t="n">
-        <v>9.818377397713244</v>
+        <v>9.828716524672853</v>
       </c>
       <c r="N15" t="n">
-        <v>176.4897683244969</v>
+        <v>176.2803531778339</v>
       </c>
       <c r="O15" t="n">
-        <v>13.28494517581826</v>
+        <v>13.27706116495039</v>
       </c>
       <c r="P15" t="n">
-        <v>379.0136250873642</v>
+        <v>378.890344479089</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27021,28 +27161,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4713441658089919</v>
+        <v>-0.4607878460925972</v>
       </c>
       <c r="J16" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K16" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07518639361207602</v>
+        <v>0.07254981472580679</v>
       </c>
       <c r="M16" t="n">
-        <v>10.24381667940066</v>
+        <v>10.24579103620939</v>
       </c>
       <c r="N16" t="n">
-        <v>156.4728752336777</v>
+        <v>156.1964570504669</v>
       </c>
       <c r="O16" t="n">
-        <v>12.50891183251676</v>
+        <v>12.497858098509</v>
       </c>
       <c r="P16" t="n">
-        <v>386.7015983178591</v>
+        <v>386.5909149557054</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27099,28 +27239,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8151841661747224</v>
+        <v>-0.8040300770014266</v>
       </c>
       <c r="J17" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K17" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03026056977232361</v>
+        <v>0.02976990231077004</v>
       </c>
       <c r="M17" t="n">
-        <v>22.01363339696134</v>
+        <v>21.89994062732482</v>
       </c>
       <c r="N17" t="n">
-        <v>1218.785433626259</v>
+        <v>1211.887657232116</v>
       </c>
       <c r="O17" t="n">
-        <v>34.91110759666985</v>
+        <v>34.81217685282143</v>
       </c>
       <c r="P17" t="n">
-        <v>372.1857736589743</v>
+        <v>372.0691417764079</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27158,7 +27298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R361"/>
+  <dimension ref="A1:R363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60072,12 +60212,196 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>-37.765078504134046,174.8322932767396</t>
+          <t>-37.765097706660015,174.83216385660145</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-37.77573235572733,174.8334064153866</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-37.77502082915272,174.83333524869292</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-37.77429855681495,174.83333348754115</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-37.77357069967939,174.8333302471724</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-37.772848372365615,174.83335588532998</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-37.77211926147207,174.83352419050635</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-37.77144118369378,174.8331646092762</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-37.7707445768027,174.83300325733026</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-37.77003187641141,174.83294005574368</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-37.769339233549914,174.83270323468955</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-37.76862733995872,174.83265624258425</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-37.76793282448707,174.83248066410076</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-37.76722861699407,174.8323901713943</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-37.76654665393371,174.83210873783108</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-37.76584776863125,174.83196645437857</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-37.765100438042374,174.8321454476966</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-37.77572827078628,174.83343455499693</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-37.77502287161589,174.8333211790199</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-37.77429677959869,174.83334588719106</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-37.77356896902965,174.83334575962706</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-37.77284827057345,174.83335712736888</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-37.772117505072615,174.8335431316738</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-37.77143911189506,174.8331818939801</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-37.770739133985494,174.83304319597173</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-37.77002637769988,174.83298492764368</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-37.769335134359466,174.83274296869038</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-37.76863255604071,174.83260272892872</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-37.76793439411606,174.83246707302925</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-37.76722438367637,174.83242184735704</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-37.76653878651346,174.83216680638063</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-37.76584460941005,174.83198857265188</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-37.765100471150014,174.83214522455836</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R363"/>
+  <dimension ref="A1:R365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22047,7 +22047,7 @@
         <v>408.26</v>
       </c>
       <c r="C363" t="n">
-        <v>404.94</v>
+        <v>401.37</v>
       </c>
       <c r="D363" t="n">
         <v>389.24</v>
@@ -22092,6 +22092,126 @@
         <v>355.87</v>
       </c>
       <c r="R363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>408.18</v>
+      </c>
+      <c r="C364" t="n">
+        <v>401.55</v>
+      </c>
+      <c r="D364" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="E364" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="F364" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="G364" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="H364" t="n">
+        <v>365.93</v>
+      </c>
+      <c r="I364" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="J364" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="K364" t="n">
+        <v>369.41</v>
+      </c>
+      <c r="L364" t="n">
+        <v>373.48</v>
+      </c>
+      <c r="M364" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="N364" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="O364" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="P364" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>408.37</v>
+      </c>
+      <c r="C365" t="n">
+        <v>401.06</v>
+      </c>
+      <c r="D365" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="E365" t="n">
+        <v>374.85</v>
+      </c>
+      <c r="F365" t="n">
+        <v>367.47</v>
+      </c>
+      <c r="G365" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="H365" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="I365" t="n">
+        <v>365.55</v>
+      </c>
+      <c r="J365" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="K365" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="L365" t="n">
+        <v>372.79</v>
+      </c>
+      <c r="M365" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="N365" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="O365" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="P365" t="n">
+        <v>382.11</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="R365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22108,7 +22228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25901,6 +26021,26 @@
       </c>
       <c r="B379" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -26069,28 +26209,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.329108023516051</v>
+        <v>-0.3106888810640389</v>
       </c>
       <c r="J2" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03166463298185496</v>
+        <v>0.02833428151421624</v>
       </c>
       <c r="M2" t="n">
-        <v>11.37371990887352</v>
+        <v>11.41856501305327</v>
       </c>
       <c r="N2" t="n">
-        <v>193.6890671589713</v>
+        <v>194.5125683312793</v>
       </c>
       <c r="O2" t="n">
-        <v>13.91722196269684</v>
+        <v>13.94677627020952</v>
       </c>
       <c r="P2" t="n">
-        <v>398.3392740753792</v>
+        <v>398.1482000825449</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26147,28 +26287,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007845401081000875</v>
+        <v>0.0172941599574653</v>
       </c>
       <c r="J3" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L3" t="n">
-        <v>1.489646869801131e-05</v>
+        <v>7.301204932252947e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>12.58551054219748</v>
+        <v>12.57054941285414</v>
       </c>
       <c r="N3" t="n">
-        <v>240.4521924583515</v>
+        <v>239.5479213340212</v>
       </c>
       <c r="O3" t="n">
-        <v>15.50652096565672</v>
+        <v>15.47733573112702</v>
       </c>
       <c r="P3" t="n">
-        <v>389.8320608482371</v>
+        <v>389.7336742540015</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26225,28 +26365,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2344222363345484</v>
+        <v>-0.2281998969188683</v>
       </c>
       <c r="J4" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02822619218347722</v>
+        <v>0.02701287645711514</v>
       </c>
       <c r="M4" t="n">
-        <v>8.519090335763797</v>
+        <v>8.510097251739907</v>
       </c>
       <c r="N4" t="n">
-        <v>108.3440567990368</v>
+        <v>107.9440899702955</v>
       </c>
       <c r="O4" t="n">
-        <v>10.40884512321309</v>
+        <v>10.38961452462484</v>
       </c>
       <c r="P4" t="n">
-        <v>388.9581929695274</v>
+        <v>388.8925833096059</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26303,28 +26443,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6838051322404923</v>
+        <v>-0.6811293656277693</v>
       </c>
       <c r="J5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1842184582773043</v>
+        <v>0.1845822785055513</v>
       </c>
       <c r="M5" t="n">
-        <v>8.835926229471955</v>
+        <v>8.802621019796687</v>
       </c>
       <c r="N5" t="n">
-        <v>118.707485824006</v>
+        <v>118.0830902636348</v>
       </c>
       <c r="O5" t="n">
-        <v>10.8952965000502</v>
+        <v>10.86660435755507</v>
       </c>
       <c r="P5" t="n">
-        <v>390.3533944522607</v>
+        <v>390.3252703974925</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26381,28 +26521,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4831189449299491</v>
+        <v>-0.4809855525331001</v>
       </c>
       <c r="J6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09516606691309171</v>
+        <v>0.09530102287708064</v>
       </c>
       <c r="M6" t="n">
-        <v>8.708778294282078</v>
+        <v>8.672160206961694</v>
       </c>
       <c r="N6" t="n">
-        <v>127.0513819958424</v>
+        <v>126.3701548789324</v>
       </c>
       <c r="O6" t="n">
-        <v>11.27170714647264</v>
+        <v>11.24144807749128</v>
       </c>
       <c r="P6" t="n">
-        <v>378.0238710116679</v>
+        <v>378.0014652111814</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26459,28 +26599,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2390937010506315</v>
+        <v>-0.246624171346328</v>
       </c>
       <c r="J7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K7" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02568622623038486</v>
+        <v>0.02749746030910294</v>
       </c>
       <c r="M7" t="n">
-        <v>8.257523304557528</v>
+        <v>8.242660412008638</v>
       </c>
       <c r="N7" t="n">
-        <v>126.2787698993694</v>
+        <v>125.8979499010059</v>
       </c>
       <c r="O7" t="n">
-        <v>11.23738269791366</v>
+        <v>11.22042556684041</v>
       </c>
       <c r="P7" t="n">
-        <v>358.7488618287774</v>
+        <v>358.8269935645919</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26537,28 +26677,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1485279101950249</v>
+        <v>-0.1483067829250817</v>
       </c>
       <c r="J8" t="n">
+        <v>364</v>
+      </c>
+      <c r="K8" t="n">
         <v>362</v>
       </c>
-      <c r="K8" t="n">
-        <v>360</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.009771749323099432</v>
+        <v>0.009844925838066065</v>
       </c>
       <c r="M8" t="n">
-        <v>8.772293643956877</v>
+        <v>8.725668062010111</v>
       </c>
       <c r="N8" t="n">
-        <v>129.0209027982641</v>
+        <v>128.3088695073843</v>
       </c>
       <c r="O8" t="n">
-        <v>11.35873684871096</v>
+        <v>11.3273505069537</v>
       </c>
       <c r="P8" t="n">
-        <v>369.3310092144878</v>
+        <v>369.3287011289052</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26615,28 +26755,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3927531348151687</v>
+        <v>-0.392645116136282</v>
       </c>
       <c r="J9" t="n">
+        <v>364</v>
+      </c>
+      <c r="K9" t="n">
         <v>362</v>
       </c>
-      <c r="K9" t="n">
-        <v>360</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09607721666076974</v>
+        <v>0.09694648488451085</v>
       </c>
       <c r="M9" t="n">
-        <v>7.296203148649836</v>
+        <v>7.256534510121648</v>
       </c>
       <c r="N9" t="n">
-        <v>83.75894151923042</v>
+        <v>83.29629833004698</v>
       </c>
       <c r="O9" t="n">
-        <v>9.151991123205399</v>
+        <v>9.126680575655476</v>
       </c>
       <c r="P9" t="n">
-        <v>375.9275550248054</v>
+        <v>375.9264272246779</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26693,28 +26833,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05773912571562251</v>
+        <v>0.05560014738537519</v>
       </c>
       <c r="J10" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K10" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009751820650281129</v>
+        <v>0.0009137370145781976</v>
       </c>
       <c r="M10" t="n">
-        <v>10.87357388665218</v>
+        <v>10.82458910129052</v>
       </c>
       <c r="N10" t="n">
-        <v>198.8962125237465</v>
+        <v>197.8257746260642</v>
       </c>
       <c r="O10" t="n">
-        <v>14.10305685033378</v>
+        <v>14.06505508791431</v>
       </c>
       <c r="P10" t="n">
-        <v>358.4575316452422</v>
+        <v>358.4797246183894</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26771,28 +26911,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1068141472197908</v>
+        <v>-0.09659815112424734</v>
       </c>
       <c r="J11" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K11" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009626067422523477</v>
+        <v>0.0007950785245314229</v>
       </c>
       <c r="M11" t="n">
-        <v>17.39430226558795</v>
+        <v>17.34149936375173</v>
       </c>
       <c r="N11" t="n">
-        <v>673.7608103992837</v>
+        <v>670.5499616963807</v>
       </c>
       <c r="O11" t="n">
-        <v>25.9569029431341</v>
+        <v>25.89497946893144</v>
       </c>
       <c r="P11" t="n">
-        <v>362.1680282026985</v>
+        <v>362.0598311909785</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26849,28 +26989,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4669847394762308</v>
+        <v>-0.4538705566572512</v>
       </c>
       <c r="J12" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06499740209077498</v>
+        <v>0.0619262557341197</v>
       </c>
       <c r="M12" t="n">
-        <v>10.8318844867985</v>
+        <v>10.83679770114481</v>
       </c>
       <c r="N12" t="n">
-        <v>179.4294797156523</v>
+        <v>179.3627656520528</v>
       </c>
       <c r="O12" t="n">
-        <v>13.39512895479742</v>
+        <v>13.3926384873203</v>
       </c>
       <c r="P12" t="n">
-        <v>372.4396293757704</v>
+        <v>372.3013289349854</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26927,28 +27067,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.02552702369352269</v>
+        <v>-0.01926355156974407</v>
       </c>
       <c r="J13" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0003469922739920417</v>
+        <v>0.0001993248591787289</v>
       </c>
       <c r="M13" t="n">
-        <v>8.077762381600664</v>
+        <v>8.067427994124138</v>
       </c>
       <c r="N13" t="n">
-        <v>109.4602905293052</v>
+        <v>109.0711310538025</v>
       </c>
       <c r="O13" t="n">
-        <v>10.46232720427464</v>
+        <v>10.44371251298131</v>
       </c>
       <c r="P13" t="n">
-        <v>371.9570539870215</v>
+        <v>371.8921048601483</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27005,28 +27145,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3603661966001701</v>
+        <v>-0.3542079223775965</v>
       </c>
       <c r="J14" t="n">
+        <v>364</v>
+      </c>
+      <c r="K14" t="n">
         <v>362</v>
       </c>
-      <c r="K14" t="n">
-        <v>360</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.04959918020376475</v>
+        <v>0.04841590274818064</v>
       </c>
       <c r="M14" t="n">
-        <v>9.460058552222433</v>
+        <v>9.442665857142936</v>
       </c>
       <c r="N14" t="n">
-        <v>145.0326904252957</v>
+        <v>144.4416467579301</v>
       </c>
       <c r="O14" t="n">
-        <v>12.04295189832193</v>
+        <v>12.01838786018866</v>
       </c>
       <c r="P14" t="n">
-        <v>373.7707525198559</v>
+        <v>373.7069356104939</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27083,28 +27223,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2775314567087797</v>
+        <v>-0.2697823344057466</v>
       </c>
       <c r="J15" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K15" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02448628156264165</v>
+        <v>0.02336602354777573</v>
       </c>
       <c r="M15" t="n">
-        <v>9.828716524672853</v>
+        <v>9.817425529325321</v>
       </c>
       <c r="N15" t="n">
-        <v>176.2803531778339</v>
+        <v>175.6261740264465</v>
       </c>
       <c r="O15" t="n">
-        <v>13.27706116495039</v>
+        <v>13.25240257562554</v>
       </c>
       <c r="P15" t="n">
-        <v>378.890344479089</v>
+        <v>378.8089641797824</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27161,28 +27301,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4607878460925972</v>
+        <v>-0.4531684042344369</v>
       </c>
       <c r="J16" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K16" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07254981472580679</v>
+        <v>0.07089234452852122</v>
       </c>
       <c r="M16" t="n">
-        <v>10.24579103620939</v>
+        <v>10.23103639687246</v>
       </c>
       <c r="N16" t="n">
-        <v>156.1964570504669</v>
+        <v>155.6395975864854</v>
       </c>
       <c r="O16" t="n">
-        <v>12.497858098509</v>
+        <v>12.4755600109368</v>
       </c>
       <c r="P16" t="n">
-        <v>386.5909149557054</v>
+        <v>386.5108420001735</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27239,28 +27379,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8040300770014266</v>
+        <v>-0.7979421215449013</v>
       </c>
       <c r="J17" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02976990231077004</v>
+        <v>0.02963087066211623</v>
       </c>
       <c r="M17" t="n">
-        <v>21.89994062732482</v>
+        <v>21.80735685442459</v>
       </c>
       <c r="N17" t="n">
-        <v>1211.887657232116</v>
+        <v>1205.285745368339</v>
       </c>
       <c r="O17" t="n">
-        <v>34.81217685282143</v>
+        <v>34.71722548488486</v>
       </c>
       <c r="P17" t="n">
-        <v>372.0691417764079</v>
+        <v>372.0051664942794</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27298,7 +27438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R363"/>
+  <dimension ref="A1:R365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60326,7 +60466,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>-37.77502287161589,174.8333211790199</t>
+          <t>-37.77501708463259,174.8333610430913</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -60400,6 +60540,190 @@
         </is>
       </c>
       <c r="R363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-37.77572814110551,174.83343544831786</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-37.775017376413594,174.83335903313827</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-37.77429682763159,174.8333455520654</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-37.773567689852456,174.83335722535392</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-37.77284782638927,174.8333625471749</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-37.77211820554181,174.83353557775595</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-37.7714378203829,174.83319266885994</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-37.77073762463045,174.83305427139214</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-37.77002430193189,174.83300186678403</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-37.76933329959004,174.83276075331239</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-37.76863120535231,174.8326165861498</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-37.76793375848137,174.83247257685167</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-37.76722469780978,174.83241949684404</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-37.76653674007003,174.83218191091444</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-37.76584176929859,174.83200845675444</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-37.76510063668824,174.8321441088671</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-37.77572844909734,174.83343332668068</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-37.77501658212081,174.833364504677</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-37.774295674841994,174.8333535950812</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-37.77356751427903,174.83335879908108</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-37.77284802071987,174.8333601760098</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-37.77211829963464,174.83353456305056</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-37.77143699973404,174.83319951539795</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-37.770737319710115,174.83305650885077</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-37.77002424694462,174.83300231550294</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-37.7693334041023,174.83275974026432</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-37.768630447648356,174.83262435971264</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-37.76793369362067,174.8324731384662</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-37.76722568508588,174.83241210951732</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-37.76653749801226,174.83217631664277</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-37.76584212032378,174.8320059991688</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-37.765103550159424,174.83212447270017</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R365"/>
+  <dimension ref="A1:R366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22217,6 +22217,66 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>411.28</v>
+      </c>
+      <c r="C366" t="n">
+        <v>403.9</v>
+      </c>
+      <c r="D366" t="n">
+        <v>391.95</v>
+      </c>
+      <c r="E366" t="n">
+        <v>376.1</v>
+      </c>
+      <c r="F366" t="n">
+        <v>367.57</v>
+      </c>
+      <c r="G366" t="n">
+        <v>345.1</v>
+      </c>
+      <c r="H366" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="I366" t="n">
+        <v>366.62</v>
+      </c>
+      <c r="J366" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="K366" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="L366" t="n">
+        <v>376.78</v>
+      </c>
+      <c r="M366" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="N366" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="O366" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="P366" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22228,7 +22288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B381"/>
+  <dimension ref="A1:B382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26041,6 +26101,16 @@
       </c>
       <c r="B381" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -26209,28 +26279,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3106888810640389</v>
+        <v>-0.3000877608309582</v>
       </c>
       <c r="J2" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02833428151421624</v>
+        <v>0.0264530586379873</v>
       </c>
       <c r="M2" t="n">
-        <v>11.41856501305327</v>
+        <v>11.44954292120706</v>
       </c>
       <c r="N2" t="n">
-        <v>194.5125683312793</v>
+        <v>195.2301328916383</v>
       </c>
       <c r="O2" t="n">
-        <v>13.94677627020952</v>
+        <v>13.972477693367</v>
       </c>
       <c r="P2" t="n">
-        <v>398.1482000825449</v>
+        <v>398.0375488472761</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26287,28 +26357,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0172941599574653</v>
+        <v>0.02414865599888069</v>
       </c>
       <c r="J3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>7.301204932252947e-05</v>
+        <v>0.0001427925792745199</v>
       </c>
       <c r="M3" t="n">
-        <v>12.57054941285414</v>
+        <v>12.57554952670619</v>
       </c>
       <c r="N3" t="n">
-        <v>239.5479213340212</v>
+        <v>239.3999714877776</v>
       </c>
       <c r="O3" t="n">
-        <v>15.47733573112702</v>
+        <v>15.47255542849266</v>
       </c>
       <c r="P3" t="n">
-        <v>389.7336742540015</v>
+        <v>389.661883965999</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26365,28 +26435,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2281998969188683</v>
+        <v>-0.2235697018820863</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K4" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02701287645711514</v>
+        <v>0.02603623750808814</v>
       </c>
       <c r="M4" t="n">
-        <v>8.510097251739907</v>
+        <v>8.514850352207471</v>
       </c>
       <c r="N4" t="n">
-        <v>107.9440899702955</v>
+        <v>107.8726959661443</v>
       </c>
       <c r="O4" t="n">
-        <v>10.38961452462484</v>
+        <v>10.38617812124095</v>
       </c>
       <c r="P4" t="n">
-        <v>388.8925833096059</v>
+        <v>388.8434628816943</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26443,28 +26513,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6811293656277693</v>
+        <v>-0.6791746622398918</v>
       </c>
       <c r="J5" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1845822785055513</v>
+        <v>0.1844666498917538</v>
       </c>
       <c r="M5" t="n">
-        <v>8.802621019796687</v>
+        <v>8.789959257039765</v>
       </c>
       <c r="N5" t="n">
-        <v>118.0830902636348</v>
+        <v>117.7954645045691</v>
       </c>
       <c r="O5" t="n">
-        <v>10.86660435755507</v>
+        <v>10.85336189871918</v>
       </c>
       <c r="P5" t="n">
-        <v>390.3252703974925</v>
+        <v>390.3046007637034</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26521,28 +26591,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4809855525331001</v>
+        <v>-0.4797974096069282</v>
       </c>
       <c r="J6" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09530102287708064</v>
+        <v>0.09532468347194811</v>
       </c>
       <c r="M6" t="n">
-        <v>8.672160206961694</v>
+        <v>8.65460137530405</v>
       </c>
       <c r="N6" t="n">
-        <v>126.3701548789324</v>
+        <v>126.0353043108967</v>
       </c>
       <c r="O6" t="n">
-        <v>11.24144807749128</v>
+        <v>11.22654462917672</v>
       </c>
       <c r="P6" t="n">
-        <v>378.0014652111814</v>
+        <v>377.9889123069834</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26599,28 +26669,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.246624171346328</v>
+        <v>-0.2501833912125803</v>
       </c>
       <c r="J7" t="n">
+        <v>365</v>
+      </c>
+      <c r="K7" t="n">
         <v>364</v>
       </c>
-      <c r="K7" t="n">
-        <v>363</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02749746030910294</v>
+        <v>0.02838874354541354</v>
       </c>
       <c r="M7" t="n">
-        <v>8.242660412008638</v>
+        <v>8.234527597263636</v>
       </c>
       <c r="N7" t="n">
-        <v>125.8979499010059</v>
+        <v>125.6925580153379</v>
       </c>
       <c r="O7" t="n">
-        <v>11.22042556684041</v>
+        <v>11.21126924194303</v>
       </c>
       <c r="P7" t="n">
-        <v>358.8269935645919</v>
+        <v>358.8641472529546</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26677,28 +26747,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1483067829250817</v>
+        <v>-0.1492426382177574</v>
       </c>
       <c r="J8" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K8" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009844925838066065</v>
+        <v>0.0100199789092098</v>
       </c>
       <c r="M8" t="n">
-        <v>8.725668062010111</v>
+        <v>8.706143301182836</v>
       </c>
       <c r="N8" t="n">
-        <v>128.3088695073843</v>
+        <v>127.9649931111028</v>
       </c>
       <c r="O8" t="n">
-        <v>11.3273505069537</v>
+        <v>11.31216129265769</v>
       </c>
       <c r="P8" t="n">
-        <v>369.3287011289052</v>
+        <v>369.3385360975023</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26755,28 +26825,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.392645116136282</v>
+        <v>-0.392084813613635</v>
       </c>
       <c r="J9" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K9" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09694648488451085</v>
+        <v>0.09715665241471039</v>
       </c>
       <c r="M9" t="n">
-        <v>7.256534510121648</v>
+        <v>7.239823249318293</v>
       </c>
       <c r="N9" t="n">
-        <v>83.29629833004698</v>
+        <v>83.07027003292789</v>
       </c>
       <c r="O9" t="n">
-        <v>9.126680575655476</v>
+        <v>9.114289332302761</v>
       </c>
       <c r="P9" t="n">
-        <v>375.9264272246779</v>
+        <v>375.920538966356</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26833,28 +26903,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05560014738537519</v>
+        <v>0.05510655958458513</v>
       </c>
       <c r="J10" t="n">
+        <v>365</v>
+      </c>
+      <c r="K10" t="n">
         <v>364</v>
       </c>
-      <c r="K10" t="n">
-        <v>363</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0009137370145781976</v>
+        <v>0.0009023327613325582</v>
       </c>
       <c r="M10" t="n">
-        <v>10.82458910129052</v>
+        <v>10.79733612061897</v>
       </c>
       <c r="N10" t="n">
-        <v>197.8257746260642</v>
+        <v>197.2849989327808</v>
       </c>
       <c r="O10" t="n">
-        <v>14.06505508791431</v>
+        <v>14.04581784492383</v>
       </c>
       <c r="P10" t="n">
-        <v>358.4797246183894</v>
+        <v>358.4848770416785</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26911,28 +26981,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09659815112424734</v>
+        <v>-0.09013499601407775</v>
       </c>
       <c r="J11" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K11" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0007950785245314229</v>
+        <v>0.0006955248816137294</v>
       </c>
       <c r="M11" t="n">
-        <v>17.34149936375173</v>
+        <v>17.32136217839501</v>
       </c>
       <c r="N11" t="n">
-        <v>670.5499616963807</v>
+        <v>669.1273641078203</v>
       </c>
       <c r="O11" t="n">
-        <v>25.89497946893144</v>
+        <v>25.86749628603086</v>
       </c>
       <c r="P11" t="n">
-        <v>362.0598311909785</v>
+        <v>361.9909665902181</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26989,28 +27059,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4538705566572512</v>
+        <v>-0.4455281084856472</v>
       </c>
       <c r="J12" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K12" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0619262557341197</v>
+        <v>0.05986634960648318</v>
       </c>
       <c r="M12" t="n">
-        <v>10.83679770114481</v>
+        <v>10.84762754260906</v>
       </c>
       <c r="N12" t="n">
-        <v>179.3627656520528</v>
+        <v>179.6185613862338</v>
       </c>
       <c r="O12" t="n">
-        <v>13.3926384873203</v>
+        <v>13.40218494821773</v>
       </c>
       <c r="P12" t="n">
-        <v>372.3013289349854</v>
+        <v>372.2128158493222</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27067,28 +27137,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.01926355156974407</v>
+        <v>-0.01401613202209851</v>
       </c>
       <c r="J13" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K13" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001993248591787289</v>
+        <v>0.0001057967043101016</v>
       </c>
       <c r="M13" t="n">
-        <v>8.067427994124138</v>
+        <v>8.073983998629579</v>
       </c>
       <c r="N13" t="n">
-        <v>109.0711310538025</v>
+        <v>109.074374356502</v>
       </c>
       <c r="O13" t="n">
-        <v>10.44371251298131</v>
+        <v>10.44386778719944</v>
       </c>
       <c r="P13" t="n">
-        <v>371.8921048601483</v>
+        <v>371.8373590657504</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27145,28 +27215,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3542079223775965</v>
+        <v>-0.346933483347636</v>
       </c>
       <c r="J14" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K14" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04841590274818064</v>
+        <v>0.04659505536539366</v>
       </c>
       <c r="M14" t="n">
-        <v>9.442665857142936</v>
+        <v>9.457402260911984</v>
       </c>
       <c r="N14" t="n">
-        <v>144.4416467579301</v>
+        <v>144.6280160061001</v>
       </c>
       <c r="O14" t="n">
-        <v>12.01838786018866</v>
+        <v>12.02613886524266</v>
       </c>
       <c r="P14" t="n">
-        <v>373.7069356104939</v>
+        <v>373.6310952708462</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27223,28 +27293,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2697823344057466</v>
+        <v>-0.2637191556363318</v>
       </c>
       <c r="J15" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K15" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02336602354777573</v>
+        <v>0.02241677583581259</v>
       </c>
       <c r="M15" t="n">
-        <v>9.817425529325321</v>
+        <v>9.823779682948343</v>
       </c>
       <c r="N15" t="n">
-        <v>175.6261740264465</v>
+        <v>175.5387065359601</v>
       </c>
       <c r="O15" t="n">
-        <v>13.25240257562554</v>
+        <v>13.2491021030091</v>
       </c>
       <c r="P15" t="n">
-        <v>378.8089641797824</v>
+        <v>378.7449044081475</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27301,28 +27371,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4531684042344369</v>
+        <v>-0.4487661451174703</v>
       </c>
       <c r="J16" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K16" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07089234452852122</v>
+        <v>0.06987141696905885</v>
       </c>
       <c r="M16" t="n">
-        <v>10.23103639687246</v>
+        <v>10.22672820436903</v>
       </c>
       <c r="N16" t="n">
-        <v>155.6395975864854</v>
+        <v>155.4168717984665</v>
       </c>
       <c r="O16" t="n">
-        <v>12.4755600109368</v>
+        <v>12.46663033054508</v>
       </c>
       <c r="P16" t="n">
-        <v>386.5108420001735</v>
+        <v>386.4642961066166</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27379,28 +27449,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7979421215449013</v>
+        <v>-0.7894264817121505</v>
       </c>
       <c r="J17" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K17" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02963087066211623</v>
+        <v>0.02915146712192551</v>
       </c>
       <c r="M17" t="n">
-        <v>21.80735685442459</v>
+        <v>21.78819831299706</v>
       </c>
       <c r="N17" t="n">
-        <v>1205.285745368339</v>
+        <v>1202.698903107374</v>
       </c>
       <c r="O17" t="n">
-        <v>34.71722548488486</v>
+        <v>34.67994958340301</v>
       </c>
       <c r="P17" t="n">
-        <v>372.0051664942794</v>
+        <v>371.9151412895157</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27438,7 +27508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R365"/>
+  <dimension ref="A1:R366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60729,6 +60799,98 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-37.775733166230715,174.83340083213017</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-37.7750211857734,174.83333279208338</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-37.77430111856582,174.83331561417074</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-37.77356908189817,174.83334474794526</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-37.77284811325824,174.83335904688352</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-37.77211856100359,174.83353174442445</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-37.771434578144934,174.833219718296</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-37.770738951033415,174.83304453844693</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-37.770025841574615,174.83298930265352</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-37.76933658591569,174.83272889857736</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-37.76863482914677,174.8325794082383</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-37.76793933649143,174.83242427799826</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-37.76723786145362,174.83232099913687</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-37.766543819240276,174.83212966041214</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-37.76584389140466,174.8319935995319</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-37.76511998803554,174.83201368452256</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R366"/>
+  <dimension ref="A1:R368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22277,6 +22277,126 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>416.37</v>
+      </c>
+      <c r="C367" t="n">
+        <v>409.52</v>
+      </c>
+      <c r="D367" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="E367" t="n">
+        <v>379.63</v>
+      </c>
+      <c r="F367" t="n">
+        <v>369.8</v>
+      </c>
+      <c r="G367" t="n">
+        <v>349.64</v>
+      </c>
+      <c r="H367" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="I367" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="J367" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="K367" t="n">
+        <v>369.01</v>
+      </c>
+      <c r="L367" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="M367" t="n">
+        <v>379.83</v>
+      </c>
+      <c r="N367" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="O367" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="P367" t="n">
+        <v>384.56</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>417.87</v>
+      </c>
+      <c r="C368" t="n">
+        <v>410.03</v>
+      </c>
+      <c r="D368" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="E368" t="n">
+        <v>381.35</v>
+      </c>
+      <c r="F368" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="G368" t="n">
+        <v>353.69</v>
+      </c>
+      <c r="H368" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="I368" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="J368" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="K368" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="L368" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="M368" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="N368" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="O368" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="P368" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22288,7 +22408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26111,6 +26231,26 @@
       </c>
       <c r="B382" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -26279,28 +26419,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3000877608309582</v>
+        <v>-0.2734392506758908</v>
       </c>
       <c r="J2" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0264530586379873</v>
+        <v>0.02185254956668026</v>
       </c>
       <c r="M2" t="n">
-        <v>11.44954292120706</v>
+        <v>11.54217034854407</v>
       </c>
       <c r="N2" t="n">
-        <v>195.2301328916383</v>
+        <v>198.1345840369246</v>
       </c>
       <c r="O2" t="n">
-        <v>13.972477693367</v>
+        <v>14.07602870261796</v>
       </c>
       <c r="P2" t="n">
-        <v>398.0375488472761</v>
+        <v>397.758164178345</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26357,28 +26497,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02414865599888069</v>
+        <v>0.04346588221048047</v>
       </c>
       <c r="J3" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001427925792745199</v>
+        <v>0.0004633614821665244</v>
       </c>
       <c r="M3" t="n">
-        <v>12.57554952670619</v>
+        <v>12.61761920437432</v>
       </c>
       <c r="N3" t="n">
-        <v>239.3999714877776</v>
+        <v>240.1404376280162</v>
       </c>
       <c r="O3" t="n">
-        <v>15.47255542849266</v>
+        <v>15.49646532690653</v>
       </c>
       <c r="P3" t="n">
-        <v>389.661883965999</v>
+        <v>389.4586742838391</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26435,28 +26575,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2235697018820863</v>
+        <v>-0.2097988498270389</v>
       </c>
       <c r="J4" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02603623750808814</v>
+        <v>0.02302400803122251</v>
       </c>
       <c r="M4" t="n">
-        <v>8.514850352207471</v>
+        <v>8.552553355447065</v>
       </c>
       <c r="N4" t="n">
-        <v>107.8726959661443</v>
+        <v>108.2980765957528</v>
       </c>
       <c r="O4" t="n">
-        <v>10.38617812124095</v>
+        <v>10.40663618061825</v>
       </c>
       <c r="P4" t="n">
-        <v>388.8434628816943</v>
+        <v>388.6967324639793</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26513,28 +26653,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6791746622398918</v>
+        <v>-0.6708545438570542</v>
       </c>
       <c r="J5" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1844666498917538</v>
+        <v>0.1818903857528673</v>
       </c>
       <c r="M5" t="n">
-        <v>8.789959257039765</v>
+        <v>8.791701707082227</v>
       </c>
       <c r="N5" t="n">
-        <v>117.7954645045691</v>
+        <v>117.5218220812601</v>
       </c>
       <c r="O5" t="n">
-        <v>10.85336189871918</v>
+        <v>10.84074822515771</v>
       </c>
       <c r="P5" t="n">
-        <v>390.3046007637034</v>
+        <v>390.2162313339477</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26591,28 +26731,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4797974096069282</v>
+        <v>-0.4729976054955143</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K6" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09532468347194811</v>
+        <v>0.09360891256908255</v>
       </c>
       <c r="M6" t="n">
-        <v>8.65460137530405</v>
+        <v>8.64339613530543</v>
       </c>
       <c r="N6" t="n">
-        <v>126.0353043108967</v>
+        <v>125.6165568415146</v>
       </c>
       <c r="O6" t="n">
-        <v>11.22654462917672</v>
+        <v>11.2078792303234</v>
       </c>
       <c r="P6" t="n">
-        <v>377.9889123069834</v>
+        <v>377.9167382572024</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26669,28 +26809,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2501833912125803</v>
+        <v>-0.2506985381523357</v>
       </c>
       <c r="J7" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K7" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02838874354541354</v>
+        <v>0.02879086941761677</v>
       </c>
       <c r="M7" t="n">
-        <v>8.234527597263636</v>
+        <v>8.199872178715191</v>
       </c>
       <c r="N7" t="n">
-        <v>125.6925580153379</v>
+        <v>125.029713389005</v>
       </c>
       <c r="O7" t="n">
-        <v>11.21126924194303</v>
+        <v>11.18166863169379</v>
       </c>
       <c r="P7" t="n">
-        <v>358.8641472529546</v>
+        <v>358.8695252791419</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26747,28 +26887,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1492426382177574</v>
+        <v>-0.1482712977567273</v>
       </c>
       <c r="J8" t="n">
+        <v>367</v>
+      </c>
+      <c r="K8" t="n">
         <v>365</v>
       </c>
-      <c r="K8" t="n">
-        <v>363</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0100199789092098</v>
+        <v>0.009994412595646929</v>
       </c>
       <c r="M8" t="n">
-        <v>8.706143301182836</v>
+        <v>8.66637594466026</v>
       </c>
       <c r="N8" t="n">
-        <v>127.9649931111028</v>
+        <v>127.2786121767234</v>
       </c>
       <c r="O8" t="n">
-        <v>11.31216129265769</v>
+        <v>11.28178231383337</v>
       </c>
       <c r="P8" t="n">
-        <v>369.3385360975023</v>
+        <v>369.3282690083637</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26825,28 +26965,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.392084813613635</v>
+        <v>-0.389733965529897</v>
       </c>
       <c r="J9" t="n">
+        <v>367</v>
+      </c>
+      <c r="K9" t="n">
         <v>365</v>
       </c>
-      <c r="K9" t="n">
-        <v>363</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09715665241471039</v>
+        <v>0.09699816205994127</v>
       </c>
       <c r="M9" t="n">
-        <v>7.239823249318293</v>
+        <v>7.213903252816847</v>
       </c>
       <c r="N9" t="n">
-        <v>83.07027003292789</v>
+        <v>82.64613040388014</v>
       </c>
       <c r="O9" t="n">
-        <v>9.114289332302761</v>
+        <v>9.090991717292461</v>
       </c>
       <c r="P9" t="n">
-        <v>375.920538966356</v>
+        <v>375.8957227513338</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26903,28 +27043,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05510655958458513</v>
+        <v>0.05404420051358486</v>
       </c>
       <c r="J10" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K10" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009023327613325582</v>
+        <v>0.0008770713460954926</v>
       </c>
       <c r="M10" t="n">
-        <v>10.79733612061897</v>
+        <v>10.74361558634915</v>
       </c>
       <c r="N10" t="n">
-        <v>197.2849989327808</v>
+        <v>196.2157440830624</v>
       </c>
       <c r="O10" t="n">
-        <v>14.04581784492383</v>
+        <v>14.00770302665867</v>
       </c>
       <c r="P10" t="n">
-        <v>358.4848770416785</v>
+        <v>358.4960073718146</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26981,28 +27121,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09013499601407775</v>
+        <v>-0.0809019201110299</v>
       </c>
       <c r="J11" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K11" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006955248816137294</v>
+        <v>0.0005659867389872231</v>
       </c>
       <c r="M11" t="n">
-        <v>17.32136217839501</v>
+        <v>17.26501232640912</v>
       </c>
       <c r="N11" t="n">
-        <v>669.1273641078203</v>
+        <v>665.8708954800377</v>
       </c>
       <c r="O11" t="n">
-        <v>25.86749628603086</v>
+        <v>25.80447433062797</v>
       </c>
       <c r="P11" t="n">
-        <v>361.9909665902181</v>
+        <v>361.89216651314</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27059,28 +27199,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4455281084856472</v>
+        <v>-0.4311414321066054</v>
       </c>
       <c r="J12" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05986634960648318</v>
+        <v>0.05650581705628555</v>
       </c>
       <c r="M12" t="n">
-        <v>10.84762754260906</v>
+        <v>10.85727322130731</v>
       </c>
       <c r="N12" t="n">
-        <v>179.6185613862338</v>
+        <v>179.7496094456901</v>
       </c>
       <c r="O12" t="n">
-        <v>13.40218494821773</v>
+        <v>13.407073112566</v>
       </c>
       <c r="P12" t="n">
-        <v>372.2128158493222</v>
+        <v>372.0595162778848</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27137,28 +27277,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.01401613202209851</v>
+        <v>-0.005221341179894609</v>
       </c>
       <c r="J13" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K13" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0001057967043101016</v>
+        <v>1.478098380736093e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>8.073983998629579</v>
+        <v>8.077331954292227</v>
       </c>
       <c r="N13" t="n">
-        <v>109.074374356502</v>
+        <v>108.905200815111</v>
       </c>
       <c r="O13" t="n">
-        <v>10.44386778719944</v>
+        <v>10.4357654637842</v>
       </c>
       <c r="P13" t="n">
-        <v>371.8373590657504</v>
+        <v>371.7451971891255</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27215,28 +27355,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.346933483347636</v>
+        <v>-0.3314095829553508</v>
       </c>
       <c r="J14" t="n">
+        <v>367</v>
+      </c>
+      <c r="K14" t="n">
         <v>365</v>
       </c>
-      <c r="K14" t="n">
-        <v>363</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.04659505536539366</v>
+        <v>0.04274889200643339</v>
       </c>
       <c r="M14" t="n">
-        <v>9.457402260911984</v>
+        <v>9.494656619935839</v>
       </c>
       <c r="N14" t="n">
-        <v>144.6280160061001</v>
+        <v>145.169679968707</v>
       </c>
       <c r="O14" t="n">
-        <v>12.02613886524266</v>
+        <v>12.04863809601347</v>
       </c>
       <c r="P14" t="n">
-        <v>373.6310952708462</v>
+        <v>373.4685405046657</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27293,28 +27433,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2637191556363318</v>
+        <v>-0.2508089625330138</v>
       </c>
       <c r="J15" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K15" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02241677583581259</v>
+        <v>0.02042705377070075</v>
       </c>
       <c r="M15" t="n">
-        <v>9.823779682948343</v>
+        <v>9.840342094075066</v>
       </c>
       <c r="N15" t="n">
-        <v>175.5387065359601</v>
+        <v>175.4790853101757</v>
       </c>
       <c r="O15" t="n">
-        <v>13.2491021030091</v>
+        <v>13.24685190187373</v>
       </c>
       <c r="P15" t="n">
-        <v>378.7449044081475</v>
+        <v>378.6079077789694</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27371,28 +27511,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4487661451174703</v>
+        <v>-0.4377005167431868</v>
       </c>
       <c r="J16" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K16" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06987141696905885</v>
+        <v>0.06708241047487673</v>
       </c>
       <c r="M16" t="n">
-        <v>10.22672820436903</v>
+        <v>10.23049051401495</v>
       </c>
       <c r="N16" t="n">
-        <v>155.4168717984665</v>
+        <v>155.230161731746</v>
       </c>
       <c r="O16" t="n">
-        <v>12.46663033054508</v>
+        <v>12.4591396866616</v>
       </c>
       <c r="P16" t="n">
-        <v>386.4642961066166</v>
+        <v>386.3467743382186</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27449,28 +27589,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7894264817121505</v>
+        <v>-0.7680030783902276</v>
       </c>
       <c r="J17" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K17" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02915146712192551</v>
+        <v>0.0278635792346047</v>
       </c>
       <c r="M17" t="n">
-        <v>21.78819831299706</v>
+        <v>21.77068682757814</v>
       </c>
       <c r="N17" t="n">
-        <v>1202.698903107374</v>
+        <v>1198.522096398958</v>
       </c>
       <c r="O17" t="n">
-        <v>34.67994958340301</v>
+        <v>34.61967787832459</v>
       </c>
       <c r="P17" t="n">
-        <v>371.9151412895157</v>
+        <v>371.6876482771941</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27508,7 +27648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R366"/>
+  <dimension ref="A1:R368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60891,6 +61031,190 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-37.775741417140296,174.8333439945723</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-37.77503029579344,174.8332700368679</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-37.774307907192714,174.83326824973275</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-37.77357350884566,174.83330506753416</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-37.77285017686106,174.83333386736717</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-37.77212330745217,174.83348055817027</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-37.77143658268283,174.83320299478603</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-37.770740262189605,174.83303491737428</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-37.77002478307038,174.83299794049327</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-37.76933283509103,174.83276525574817</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-37.76863291842024,174.8325990111376</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-37.76793662532155,174.83244775348848</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-37.767239043185846,174.8323121567272</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-37.76654466813281,174.83212339482654</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-37.76584602946454,174.8319786306</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-37.765124341655174,174.83198434182412</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>-37.775743848640886,174.83332724479817</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>-37.7750311225018,174.83326434199878</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>-37.774309075987425,174.83326009500544</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-37.773575665880415,174.83328573316763</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-37.77285421151301,174.83328463745607</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-37.77212754160021,174.8334348964174</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-37.77144014779474,174.83317325162827</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-37.77074135990115,174.83302686252247</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-37.77002665263586,174.83298268404883</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-37.7693322660795,174.8327707712319</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-37.768632193661055,174.8326064467198</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-37.76793801333733,174.8324357349363</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>-37.76724022491742,174.83230331431724</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-37.766545835359516,174.8321147796461</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>-37.76584928441775,174.83195584207502</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>-37.765130797579715,174.83194082983096</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R368"/>
+  <dimension ref="A1:R369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22397,6 +22397,66 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>414.48</v>
+      </c>
+      <c r="C369" t="n">
+        <v>408.14</v>
+      </c>
+      <c r="D369" t="n">
+        <v>394.69</v>
+      </c>
+      <c r="E369" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="F369" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="G369" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="H369" t="n">
+        <v>367.08</v>
+      </c>
+      <c r="I369" t="n">
+        <v>367.98</v>
+      </c>
+      <c r="J369" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="K369" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="L369" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="M369" t="n">
+        <v>379.05</v>
+      </c>
+      <c r="N369" t="n">
+        <v>377.56</v>
+      </c>
+      <c r="O369" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="P369" t="n">
+        <v>384.39</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22408,7 +22468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B384"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26251,6 +26311,16 @@
       </c>
       <c r="B384" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -26419,28 +26489,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2734392506758908</v>
+        <v>-0.26161257476963</v>
       </c>
       <c r="J2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K2" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02185254956668026</v>
+        <v>0.01998767710109017</v>
       </c>
       <c r="M2" t="n">
-        <v>11.54217034854407</v>
+        <v>11.57923837552334</v>
       </c>
       <c r="N2" t="n">
-        <v>198.1345840369246</v>
+        <v>199.164568802562</v>
       </c>
       <c r="O2" t="n">
-        <v>14.07602870261796</v>
+        <v>14.11256776077841</v>
       </c>
       <c r="P2" t="n">
-        <v>397.758164178345</v>
+        <v>397.6336320908437</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26497,28 +26567,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04346588221048047</v>
+        <v>0.05216030152285202</v>
       </c>
       <c r="J3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004633614821665244</v>
+        <v>0.0006683281178668787</v>
       </c>
       <c r="M3" t="n">
-        <v>12.61761920437432</v>
+        <v>12.63282144678797</v>
       </c>
       <c r="N3" t="n">
-        <v>240.1404376280162</v>
+        <v>240.3184438597854</v>
       </c>
       <c r="O3" t="n">
-        <v>15.49646532690653</v>
+        <v>15.50220770921953</v>
       </c>
       <c r="P3" t="n">
-        <v>389.4586742838391</v>
+        <v>389.3668139367015</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26575,28 +26645,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2097988498270389</v>
+        <v>-0.2039508786858719</v>
       </c>
       <c r="J4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02302400803122251</v>
+        <v>0.02182607860567509</v>
       </c>
       <c r="M4" t="n">
-        <v>8.552553355447065</v>
+        <v>8.565242061368467</v>
       </c>
       <c r="N4" t="n">
-        <v>108.2980765957528</v>
+        <v>108.3687768521795</v>
       </c>
       <c r="O4" t="n">
-        <v>10.40663618061825</v>
+        <v>10.41003250966007</v>
       </c>
       <c r="P4" t="n">
-        <v>388.6967324639793</v>
+        <v>388.6341537669807</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26653,28 +26723,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6708545438570542</v>
+        <v>-0.6671174530276732</v>
       </c>
       <c r="J5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K5" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1818903857528673</v>
+        <v>0.1808309769429802</v>
       </c>
       <c r="M5" t="n">
-        <v>8.791701707082227</v>
+        <v>8.790161615794828</v>
       </c>
       <c r="N5" t="n">
-        <v>117.5218220812601</v>
+        <v>117.3491959005636</v>
       </c>
       <c r="O5" t="n">
-        <v>10.84074822515771</v>
+        <v>10.83278338658</v>
       </c>
       <c r="P5" t="n">
-        <v>390.2162313339477</v>
+        <v>390.1763730245298</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26731,28 +26801,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4729976054955143</v>
+        <v>-0.4690452306341194</v>
       </c>
       <c r="J6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K6" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09360891256908255</v>
+        <v>0.09252937413696349</v>
       </c>
       <c r="M6" t="n">
-        <v>8.64339613530543</v>
+        <v>8.640642682254926</v>
       </c>
       <c r="N6" t="n">
-        <v>125.6165568415146</v>
+        <v>125.4409331315466</v>
       </c>
       <c r="O6" t="n">
-        <v>11.2078792303234</v>
+        <v>11.20004165758086</v>
       </c>
       <c r="P6" t="n">
-        <v>377.9167382572024</v>
+        <v>377.8746227805845</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26809,28 +26879,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2506985381523357</v>
+        <v>-0.2498793811928452</v>
       </c>
       <c r="J7" t="n">
+        <v>368</v>
+      </c>
+      <c r="K7" t="n">
         <v>367</v>
       </c>
-      <c r="K7" t="n">
-        <v>366</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02879086941761677</v>
+        <v>0.02875383290780464</v>
       </c>
       <c r="M7" t="n">
-        <v>8.199872178715191</v>
+        <v>8.183208652130968</v>
       </c>
       <c r="N7" t="n">
-        <v>125.029713389005</v>
+        <v>124.6965263498931</v>
       </c>
       <c r="O7" t="n">
-        <v>11.18166863169379</v>
+        <v>11.16675988592453</v>
       </c>
       <c r="P7" t="n">
-        <v>358.8695252791419</v>
+        <v>358.8608998354345</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26887,28 +26957,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1482712977567273</v>
+        <v>-0.1474178943296952</v>
       </c>
       <c r="J8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009994412595646929</v>
+        <v>0.009932184310053604</v>
       </c>
       <c r="M8" t="n">
-        <v>8.66637594466026</v>
+        <v>8.647945605822041</v>
       </c>
       <c r="N8" t="n">
-        <v>127.2786121767234</v>
+        <v>126.9388882378255</v>
       </c>
       <c r="O8" t="n">
-        <v>11.28178231383337</v>
+        <v>11.26671594733024</v>
       </c>
       <c r="P8" t="n">
-        <v>369.3282690083637</v>
+        <v>369.3192229839058</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26965,28 +27035,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.389733965529897</v>
+        <v>-0.3884894410140783</v>
       </c>
       <c r="J9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09699816205994127</v>
+        <v>0.09688394485802831</v>
       </c>
       <c r="M9" t="n">
-        <v>7.213903252816847</v>
+        <v>7.201455648912826</v>
       </c>
       <c r="N9" t="n">
-        <v>82.64613040388014</v>
+        <v>82.43740228375204</v>
       </c>
       <c r="O9" t="n">
-        <v>9.090991717292461</v>
+        <v>9.079504517524732</v>
       </c>
       <c r="P9" t="n">
-        <v>375.8957227513338</v>
+        <v>375.8825308671067</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27043,28 +27113,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05404420051358486</v>
+        <v>0.05274305349961583</v>
       </c>
       <c r="J10" t="n">
+        <v>368</v>
+      </c>
+      <c r="K10" t="n">
         <v>367</v>
       </c>
-      <c r="K10" t="n">
-        <v>366</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0008770713460954926</v>
+        <v>0.0008397206001916624</v>
       </c>
       <c r="M10" t="n">
-        <v>10.74361558634915</v>
+        <v>10.72072870929036</v>
       </c>
       <c r="N10" t="n">
-        <v>196.2157440830624</v>
+        <v>195.7000021277144</v>
       </c>
       <c r="O10" t="n">
-        <v>14.00770302665867</v>
+        <v>13.98928168733886</v>
       </c>
       <c r="P10" t="n">
-        <v>358.4960073718146</v>
+        <v>358.5097080065881</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27121,28 +27191,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0809019201110299</v>
+        <v>-0.07762206142991483</v>
       </c>
       <c r="J11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K11" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0005659867389872231</v>
+        <v>0.0005237276786510536</v>
       </c>
       <c r="M11" t="n">
-        <v>17.26501232640912</v>
+        <v>17.23118535990816</v>
       </c>
       <c r="N11" t="n">
-        <v>665.8708954800377</v>
+        <v>664.1431586619444</v>
       </c>
       <c r="O11" t="n">
-        <v>25.80447433062797</v>
+        <v>25.77097512050998</v>
       </c>
       <c r="P11" t="n">
-        <v>361.89216651314</v>
+        <v>361.8569179724936</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27199,28 +27269,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4311414321066054</v>
+        <v>-0.425013995011905</v>
       </c>
       <c r="J12" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K12" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05650581705628555</v>
+        <v>0.05515560704811995</v>
       </c>
       <c r="M12" t="n">
-        <v>10.85727322130731</v>
+        <v>10.85664667206981</v>
       </c>
       <c r="N12" t="n">
-        <v>179.7496094456901</v>
+        <v>179.6633446215194</v>
       </c>
       <c r="O12" t="n">
-        <v>13.407073112566</v>
+        <v>13.403855587909</v>
       </c>
       <c r="P12" t="n">
-        <v>372.0595162778848</v>
+        <v>371.9939413435596</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27277,28 +27347,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.005221341179894609</v>
+        <v>-0.001542026009349651</v>
       </c>
       <c r="J13" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K13" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L13" t="n">
-        <v>1.478098380736093e-05</v>
+        <v>1.294278397678816e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>8.077331954292227</v>
+        <v>8.07495093113374</v>
       </c>
       <c r="N13" t="n">
-        <v>108.905200815111</v>
+        <v>108.757628600309</v>
       </c>
       <c r="O13" t="n">
-        <v>10.4357654637842</v>
+        <v>10.42869256428192</v>
       </c>
       <c r="P13" t="n">
-        <v>371.7451971891255</v>
+        <v>371.7064760964857</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27355,28 +27425,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3314095829553508</v>
+        <v>-0.3250160531688749</v>
       </c>
       <c r="J14" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K14" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04274889200643339</v>
+        <v>0.0412684980602287</v>
       </c>
       <c r="M14" t="n">
-        <v>9.494656619935839</v>
+        <v>9.505319119328867</v>
       </c>
       <c r="N14" t="n">
-        <v>145.169679968707</v>
+        <v>145.2276531931935</v>
       </c>
       <c r="O14" t="n">
-        <v>12.04863809601347</v>
+        <v>12.05104365576664</v>
       </c>
       <c r="P14" t="n">
-        <v>373.4685405046657</v>
+        <v>373.401304096403</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27433,28 +27503,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2508089625330138</v>
+        <v>-0.2442535922071302</v>
       </c>
       <c r="J15" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K15" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02042705377070075</v>
+        <v>0.01944343188236175</v>
       </c>
       <c r="M15" t="n">
-        <v>9.840342094075066</v>
+        <v>9.848982599765568</v>
       </c>
       <c r="N15" t="n">
-        <v>175.4790853101757</v>
+        <v>175.4669284533311</v>
       </c>
       <c r="O15" t="n">
-        <v>13.24685190187373</v>
+        <v>13.24639303559015</v>
       </c>
       <c r="P15" t="n">
-        <v>378.6079077789694</v>
+        <v>378.5380476968533</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27511,28 +27581,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4377005167431868</v>
+        <v>-0.432829492111091</v>
       </c>
       <c r="J16" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K16" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06708241047487673</v>
+        <v>0.06591664012541498</v>
       </c>
       <c r="M16" t="n">
-        <v>10.23049051401495</v>
+        <v>10.22853795206712</v>
       </c>
       <c r="N16" t="n">
-        <v>155.230161731746</v>
+        <v>155.0614915745125</v>
       </c>
       <c r="O16" t="n">
-        <v>12.4591396866616</v>
+        <v>12.45236891416699</v>
       </c>
       <c r="P16" t="n">
-        <v>386.3467743382186</v>
+        <v>386.2948224185944</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27589,28 +27659,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7680030783902276</v>
+        <v>-0.7578596965873853</v>
       </c>
       <c r="J17" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0278635792346047</v>
+        <v>0.02726795406060845</v>
       </c>
       <c r="M17" t="n">
-        <v>21.77068682757814</v>
+        <v>21.75879726366146</v>
       </c>
       <c r="N17" t="n">
-        <v>1198.522096398958</v>
+        <v>1196.320538790244</v>
       </c>
       <c r="O17" t="n">
-        <v>34.61967787832459</v>
+        <v>34.58786693033041</v>
       </c>
       <c r="P17" t="n">
-        <v>371.6876482771941</v>
+        <v>371.5794802946439</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27648,7 +27718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R368"/>
+  <dimension ref="A1:R369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61215,6 +61285,98 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-37.77573835344618,174.83336509928594</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-37.77502805881649,174.83328544651314</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-37.77430550555799,174.83328500602087</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-37.77357362171383,174.8333040558522</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-37.77285327688216,174.83329604163328</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-37.77212768796552,174.83343331798633</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-37.77143936750673,174.83317976145176</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-37.77074102448934,174.83302932372723</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-37.77002355960368,174.83300792448955</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-37.769329630043174,174.8327963225534</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-37.76863042568591,174.83262458503327</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-37.76793561349619,174.83245651467573</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-37.76723582707763,174.8323362215123</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-37.766545835359516,174.8321147796461</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-37.76584575821824,174.83198052964366</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-37.765126146004924,174.83197218078072</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R369"/>
+  <dimension ref="A1:R371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22457,6 +22457,126 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>415.53</v>
+      </c>
+      <c r="C370" t="n">
+        <v>408.57</v>
+      </c>
+      <c r="D370" t="n">
+        <v>394.95</v>
+      </c>
+      <c r="E370" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="F370" t="n">
+        <v>374.57</v>
+      </c>
+      <c r="G370" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="H370" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="I370" t="n">
+        <v>367.98</v>
+      </c>
+      <c r="J370" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="K370" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="L370" t="n">
+        <v>371.41</v>
+      </c>
+      <c r="M370" t="n">
+        <v>378.41</v>
+      </c>
+      <c r="N370" t="n">
+        <v>378.07</v>
+      </c>
+      <c r="O370" t="n">
+        <v>385.99</v>
+      </c>
+      <c r="P370" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>415.86</v>
+      </c>
+      <c r="C371" t="n">
+        <v>408.7</v>
+      </c>
+      <c r="D371" t="n">
+        <v>395.45</v>
+      </c>
+      <c r="E371" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="F371" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="G371" t="n">
+        <v>354.25</v>
+      </c>
+      <c r="H371" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="I371" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="J371" t="n">
+        <v>357.85</v>
+      </c>
+      <c r="K371" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="L371" t="n">
+        <v>370.3</v>
+      </c>
+      <c r="M371" t="n">
+        <v>378.12</v>
+      </c>
+      <c r="N371" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="O371" t="n">
+        <v>386.51</v>
+      </c>
+      <c r="P371" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22468,7 +22588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B385"/>
+  <dimension ref="A1:B387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26321,6 +26441,26 @@
       </c>
       <c r="B385" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>
@@ -26489,28 +26629,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.26161257476963</v>
+        <v>-0.2371733408158018</v>
       </c>
       <c r="J2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K2" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01998767710109017</v>
+        <v>0.01638209955170433</v>
       </c>
       <c r="M2" t="n">
-        <v>11.57923837552334</v>
+        <v>11.66111673531388</v>
       </c>
       <c r="N2" t="n">
-        <v>199.164568802562</v>
+        <v>201.458408400755</v>
       </c>
       <c r="O2" t="n">
-        <v>14.11256776077841</v>
+        <v>14.1936044893732</v>
       </c>
       <c r="P2" t="n">
-        <v>397.6336320908437</v>
+        <v>397.3754526581797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26567,28 +26707,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05216030152285202</v>
+        <v>0.06972377370672063</v>
       </c>
       <c r="J3" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K3" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006683281178668787</v>
+        <v>0.001197549546389398</v>
       </c>
       <c r="M3" t="n">
-        <v>12.63282144678797</v>
+        <v>12.66421380394903</v>
       </c>
       <c r="N3" t="n">
-        <v>240.3184438597854</v>
+        <v>240.7255111317297</v>
       </c>
       <c r="O3" t="n">
-        <v>15.50220770921953</v>
+        <v>15.51533148636308</v>
       </c>
       <c r="P3" t="n">
-        <v>389.3668139367015</v>
+        <v>389.1806456257029</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26645,28 +26785,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2039508786858719</v>
+        <v>-0.191945364555421</v>
       </c>
       <c r="J4" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02182607860567509</v>
+        <v>0.01944339244948734</v>
       </c>
       <c r="M4" t="n">
-        <v>8.565242061368467</v>
+        <v>8.592357319929802</v>
       </c>
       <c r="N4" t="n">
-        <v>108.3687768521795</v>
+        <v>108.5582902878202</v>
       </c>
       <c r="O4" t="n">
-        <v>10.41003250966007</v>
+        <v>10.4191309756534</v>
       </c>
       <c r="P4" t="n">
-        <v>388.6341537669807</v>
+        <v>388.505268379778</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26723,28 +26863,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6671174530276732</v>
+        <v>-0.657541854759334</v>
       </c>
       <c r="J5" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1808309769429802</v>
+        <v>0.1775076779235739</v>
       </c>
       <c r="M5" t="n">
-        <v>8.790161615794828</v>
+        <v>8.799489705413603</v>
       </c>
       <c r="N5" t="n">
-        <v>117.3491959005636</v>
+        <v>117.2081951210966</v>
       </c>
       <c r="O5" t="n">
-        <v>10.83278338658</v>
+        <v>10.82627337180697</v>
       </c>
       <c r="P5" t="n">
-        <v>390.1763730245298</v>
+        <v>390.0739115812327</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26801,28 +26941,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4690452306341194</v>
+        <v>-0.4594186535642334</v>
       </c>
       <c r="J6" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09252937413696349</v>
+        <v>0.08964175728920731</v>
       </c>
       <c r="M6" t="n">
-        <v>8.640642682254926</v>
+        <v>8.645226735741836</v>
       </c>
       <c r="N6" t="n">
-        <v>125.4409331315466</v>
+        <v>125.2623528908958</v>
       </c>
       <c r="O6" t="n">
-        <v>11.20004165758086</v>
+        <v>11.19206651565723</v>
       </c>
       <c r="P6" t="n">
-        <v>377.8746227805845</v>
+        <v>377.7717146007994</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26879,28 +27019,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2498793811928452</v>
+        <v>-0.2479872362255548</v>
       </c>
       <c r="J7" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K7" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02875383290780464</v>
+        <v>0.02861885514777596</v>
       </c>
       <c r="M7" t="n">
-        <v>8.183208652130968</v>
+        <v>8.151833057668023</v>
       </c>
       <c r="N7" t="n">
-        <v>124.6965263498931</v>
+        <v>124.040891103308</v>
       </c>
       <c r="O7" t="n">
-        <v>11.16675988592453</v>
+        <v>11.13736463905658</v>
       </c>
       <c r="P7" t="n">
-        <v>358.8608998354345</v>
+        <v>358.8409104536597</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26957,28 +27097,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1474178943296952</v>
+        <v>-0.1454966079776804</v>
       </c>
       <c r="J8" t="n">
+        <v>370</v>
+      </c>
+      <c r="K8" t="n">
         <v>368</v>
       </c>
-      <c r="K8" t="n">
-        <v>366</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.009932184310053604</v>
+        <v>0.00977758816988894</v>
       </c>
       <c r="M8" t="n">
-        <v>8.647945605822041</v>
+        <v>8.612630703414004</v>
       </c>
       <c r="N8" t="n">
-        <v>126.9388882378255</v>
+        <v>126.2698325347153</v>
       </c>
       <c r="O8" t="n">
-        <v>11.26671594733024</v>
+        <v>11.23698502867719</v>
       </c>
       <c r="P8" t="n">
-        <v>369.3192229839058</v>
+        <v>369.2987895539417</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27035,28 +27175,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3884894410140783</v>
+        <v>-0.3856404996928515</v>
       </c>
       <c r="J9" t="n">
+        <v>370</v>
+      </c>
+      <c r="K9" t="n">
         <v>368</v>
       </c>
-      <c r="K9" t="n">
-        <v>366</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09688394485802831</v>
+        <v>0.09647161818095751</v>
       </c>
       <c r="M9" t="n">
-        <v>7.201455648912826</v>
+        <v>7.178769253888852</v>
       </c>
       <c r="N9" t="n">
-        <v>82.43740228375204</v>
+        <v>82.03522367437513</v>
       </c>
       <c r="O9" t="n">
-        <v>9.079504517524732</v>
+        <v>9.057329831378294</v>
       </c>
       <c r="P9" t="n">
-        <v>375.8825308671067</v>
+        <v>375.8522314232977</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27113,28 +27253,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05274305349961583</v>
+        <v>0.05063062969947663</v>
       </c>
       <c r="J10" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K10" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008397206001916624</v>
+        <v>0.0007819322996133193</v>
       </c>
       <c r="M10" t="n">
-        <v>10.72072870929036</v>
+        <v>10.67288128697937</v>
       </c>
       <c r="N10" t="n">
-        <v>195.7000021277144</v>
+        <v>194.6644246731086</v>
       </c>
       <c r="O10" t="n">
-        <v>13.98928168733886</v>
+        <v>13.95221934579257</v>
       </c>
       <c r="P10" t="n">
-        <v>358.5097080065881</v>
+        <v>358.5320216086637</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27191,28 +27331,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07762206142991483</v>
+        <v>-0.07364674993402678</v>
       </c>
       <c r="J11" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K11" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0005237276786510536</v>
+        <v>0.0004764276003172974</v>
       </c>
       <c r="M11" t="n">
-        <v>17.23118535990816</v>
+        <v>17.15301159665058</v>
       </c>
       <c r="N11" t="n">
-        <v>664.1431586619444</v>
+        <v>660.5720754444778</v>
       </c>
       <c r="O11" t="n">
-        <v>25.77097512050998</v>
+        <v>25.70159674892745</v>
       </c>
       <c r="P11" t="n">
-        <v>361.8569179724936</v>
+        <v>361.8140656533428</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27269,28 +27409,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.425013995011905</v>
+        <v>-0.4148472870835317</v>
       </c>
       <c r="J12" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K12" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05515560704811995</v>
+        <v>0.0530550153541528</v>
       </c>
       <c r="M12" t="n">
-        <v>10.85664667206981</v>
+        <v>10.84523545399469</v>
       </c>
       <c r="N12" t="n">
-        <v>179.6633446215194</v>
+        <v>179.2461903269817</v>
       </c>
       <c r="O12" t="n">
-        <v>13.403855587909</v>
+        <v>13.38828556339391</v>
       </c>
       <c r="P12" t="n">
-        <v>371.9939413435596</v>
+        <v>371.8847969925396</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27347,28 +27487,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.001542026009349651</v>
+        <v>0.004912959907902844</v>
       </c>
       <c r="J13" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K13" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L13" t="n">
-        <v>1.294278397678816e-06</v>
+        <v>1.324873070551735e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>8.07495093113374</v>
+        <v>8.065426208999739</v>
       </c>
       <c r="N13" t="n">
-        <v>108.757628600309</v>
+        <v>108.3986189174327</v>
       </c>
       <c r="O13" t="n">
-        <v>10.42869256428192</v>
+        <v>10.41146574298896</v>
       </c>
       <c r="P13" t="n">
-        <v>371.7064760964857</v>
+        <v>371.6383263597832</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27425,28 +27565,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3250160531688749</v>
+        <v>-0.311713189522409</v>
       </c>
       <c r="J14" t="n">
+        <v>370</v>
+      </c>
+      <c r="K14" t="n">
         <v>368</v>
       </c>
-      <c r="K14" t="n">
-        <v>366</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.0412684980602287</v>
+        <v>0.03822262503661644</v>
       </c>
       <c r="M14" t="n">
-        <v>9.505319119328867</v>
+        <v>9.529103037471382</v>
       </c>
       <c r="N14" t="n">
-        <v>145.2276531931935</v>
+        <v>145.4289343840381</v>
       </c>
       <c r="O14" t="n">
-        <v>12.05104365576664</v>
+        <v>12.05939195747605</v>
       </c>
       <c r="P14" t="n">
-        <v>373.401304096403</v>
+        <v>373.2609546365805</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27503,28 +27643,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2442535922071302</v>
+        <v>-0.2301579785850346</v>
       </c>
       <c r="J15" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K15" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01944343188236175</v>
+        <v>0.01737509715357777</v>
       </c>
       <c r="M15" t="n">
-        <v>9.848982599765568</v>
+        <v>9.871354237158238</v>
       </c>
       <c r="N15" t="n">
-        <v>175.4669284533311</v>
+        <v>175.6020122620515</v>
       </c>
       <c r="O15" t="n">
-        <v>13.24639303559015</v>
+        <v>13.25149094487302</v>
       </c>
       <c r="P15" t="n">
-        <v>378.5380476968533</v>
+        <v>378.3873481271893</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27581,28 +27721,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.432829492111091</v>
+        <v>-0.4219643604681804</v>
       </c>
       <c r="J16" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K16" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06591664012541498</v>
+        <v>0.06322617281108833</v>
       </c>
       <c r="M16" t="n">
-        <v>10.22853795206712</v>
+        <v>10.23032037604099</v>
       </c>
       <c r="N16" t="n">
-        <v>155.0614915745125</v>
+        <v>154.8625555951456</v>
       </c>
       <c r="O16" t="n">
-        <v>12.45236891416699</v>
+        <v>12.44437847363803</v>
       </c>
       <c r="P16" t="n">
-        <v>386.2948224185944</v>
+        <v>386.1785609817075</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27659,28 +27799,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7578596965873853</v>
+        <v>-0.7427824730225721</v>
       </c>
       <c r="J17" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K17" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02726795406060845</v>
+        <v>0.02646598699876468</v>
       </c>
       <c r="M17" t="n">
-        <v>21.75879726366146</v>
+        <v>21.70990547892395</v>
       </c>
       <c r="N17" t="n">
-        <v>1196.320538790244</v>
+        <v>1190.986523767648</v>
       </c>
       <c r="O17" t="n">
-        <v>34.58786693033041</v>
+        <v>34.5106726067118</v>
       </c>
       <c r="P17" t="n">
-        <v>371.5794802946439</v>
+        <v>371.4182032991179</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27718,7 +27858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R369"/>
+  <dimension ref="A1:R371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61377,6 +61517,190 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-37.775740055498936,174.83335337444524</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-37.77502875584576,174.8332806449571</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-37.77430592184152,174.83328210159766</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-37.77357571604399,174.83328528353118</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-37.7728545909173,174.8332800080375</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-37.77212782387611,174.83343185230032</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-37.77143935405347,174.83317987369009</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-37.77074102448934,174.83302932372723</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-37.77002405448918,174.8330038860192</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>-37.76932740043987,174.83281793424223</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-37.76862893223892,174.83263990683767</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-37.767934783280026,174.832463703342</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>-37.76723658996885,174.83233051312163</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>-37.76654729060232,174.83210403864152</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>-37.765847018715476,174.83197170467596</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>-37.765121262670185,174.8320050936949</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-37.775740590429564,174.8333496894952</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-37.7750289665755,174.83327919332388</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-37.77430672238654,174.83327651616838</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-37.77357707045951,174.8332731433469</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-37.77285538674035,174.8332702975496</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-37.772128127061286,174.8334285826931</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-37.77144004016882,174.83317414953498</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-37.77074219843044,174.8330207095105</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-37.7700243156787,174.83300175460428</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-37.7693260882236,174.8328306536209</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-37.76862771332118,174.83265241213343</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-37.767934407088205,174.83246696070634</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-37.76723726310795,174.83232547630624</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-37.76654807885843,174.83209822059715</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>-37.76584859832503,174.8319606455388</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-37.76511470739976,174.83204927509098</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0223/nzd0223.xlsx
+++ b/data/nzd0223/nzd0223.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R371"/>
+  <dimension ref="A1:R373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22577,6 +22577,126 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>414.86</v>
+      </c>
+      <c r="C372" t="n">
+        <v>407.23</v>
+      </c>
+      <c r="D372" t="n">
+        <v>394.28</v>
+      </c>
+      <c r="E372" t="n">
+        <v>383.55</v>
+      </c>
+      <c r="F372" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="G372" t="n">
+        <v>354.79</v>
+      </c>
+      <c r="H372" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="I372" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="J372" t="n">
+        <v>361.27</v>
+      </c>
+      <c r="K372" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="L372" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="M372" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="N372" t="n">
+        <v>381.96</v>
+      </c>
+      <c r="O372" t="n">
+        <v>389.46</v>
+      </c>
+      <c r="P372" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>365.41</v>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>420.49</v>
+      </c>
+      <c r="C373" t="n">
+        <v>408.35</v>
+      </c>
+      <c r="D373" t="n">
+        <v>397.39</v>
+      </c>
+      <c r="E373" t="n">
+        <v>390.55</v>
+      </c>
+      <c r="F373" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="G373" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="H373" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="I373" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="J373" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="K373" t="n">
+        <v>368.18</v>
+      </c>
+      <c r="L373" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="M373" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="N373" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="O373" t="n">
+        <v>395</v>
+      </c>
+      <c r="P373" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22588,7 +22708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B387"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26461,6 +26581,26 @@
       </c>
       <c r="B387" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -26629,28 +26769,28 @@
         <v>0.0455</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2371733408158018</v>
+        <v>-0.211309188490014</v>
       </c>
       <c r="J2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K2" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01638209955170433</v>
+        <v>0.0129380474677423</v>
       </c>
       <c r="M2" t="n">
-        <v>11.66111673531388</v>
+        <v>11.75322755814515</v>
       </c>
       <c r="N2" t="n">
-        <v>201.458408400755</v>
+        <v>204.2157220685902</v>
       </c>
       <c r="O2" t="n">
-        <v>14.1936044893732</v>
+        <v>14.29040664461968</v>
       </c>
       <c r="P2" t="n">
-        <v>397.3754526581797</v>
+        <v>397.1007129874924</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26707,28 +26847,28 @@
         <v>0.0402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06972377370672063</v>
+        <v>0.08607227605030771</v>
       </c>
       <c r="J3" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K3" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001197549546389398</v>
+        <v>0.001831606132166042</v>
       </c>
       <c r="M3" t="n">
-        <v>12.66421380394903</v>
+        <v>12.68819606910504</v>
       </c>
       <c r="N3" t="n">
-        <v>240.7255111317297</v>
+        <v>240.9174648583167</v>
       </c>
       <c r="O3" t="n">
-        <v>15.51533148636308</v>
+        <v>15.52151619070498</v>
       </c>
       <c r="P3" t="n">
-        <v>389.1806456257029</v>
+        <v>389.0064167624596</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26785,28 +26925,28 @@
         <v>0.0548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.191945364555421</v>
+        <v>-0.179546727240269</v>
       </c>
       <c r="J4" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01944339244948734</v>
+        <v>0.01709877407144067</v>
       </c>
       <c r="M4" t="n">
-        <v>8.592357319929802</v>
+        <v>8.621828581435878</v>
       </c>
       <c r="N4" t="n">
-        <v>108.5582902878202</v>
+        <v>108.8204009888117</v>
       </c>
       <c r="O4" t="n">
-        <v>10.4191309756534</v>
+        <v>10.43170173024573</v>
       </c>
       <c r="P4" t="n">
-        <v>388.505268379778</v>
+        <v>388.3714383816675</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26863,28 +27003,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.657541854759334</v>
+        <v>-0.6430376431066952</v>
       </c>
       <c r="J5" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K5" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1775076779235739</v>
+        <v>0.1711099727808835</v>
       </c>
       <c r="M5" t="n">
-        <v>8.799489705413603</v>
+        <v>8.837352866246508</v>
       </c>
       <c r="N5" t="n">
-        <v>117.2081951210966</v>
+        <v>117.7933950690889</v>
       </c>
       <c r="O5" t="n">
-        <v>10.82627337180697</v>
+        <v>10.85326656215026</v>
       </c>
       <c r="P5" t="n">
-        <v>390.0739115812327</v>
+        <v>389.9178608150847</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26941,28 +27081,28 @@
         <v>0.0672</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4594186535642334</v>
+        <v>-0.4457701458317324</v>
       </c>
       <c r="J6" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K6" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08964175728920731</v>
+        <v>0.08500847736118899</v>
       </c>
       <c r="M6" t="n">
-        <v>8.645226735741836</v>
+        <v>8.671974896812594</v>
       </c>
       <c r="N6" t="n">
-        <v>125.2623528908958</v>
+        <v>125.6408237792978</v>
       </c>
       <c r="O6" t="n">
-        <v>11.19206651565723</v>
+        <v>11.20896176188044</v>
       </c>
       <c r="P6" t="n">
-        <v>377.7717146007994</v>
+        <v>377.6250224857647</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27019,28 +27159,28 @@
         <v>0.1755</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2479872362255548</v>
+        <v>-0.2445117671453497</v>
       </c>
       <c r="J7" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02861885514777596</v>
+        <v>0.02811419421247519</v>
       </c>
       <c r="M7" t="n">
-        <v>8.151833057668023</v>
+        <v>8.131578331246077</v>
       </c>
       <c r="N7" t="n">
-        <v>124.040891103308</v>
+        <v>123.4454789495738</v>
       </c>
       <c r="O7" t="n">
-        <v>11.13736463905658</v>
+        <v>11.11060209662707</v>
       </c>
       <c r="P7" t="n">
-        <v>358.8409104536597</v>
+        <v>358.8039903559766</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27097,28 +27237,28 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1454966079776804</v>
+        <v>-0.141560730940749</v>
       </c>
       <c r="J8" t="n">
+        <v>372</v>
+      </c>
+      <c r="K8" t="n">
         <v>370</v>
       </c>
-      <c r="K8" t="n">
-        <v>368</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.00977758816988894</v>
+        <v>0.0093508789828054</v>
       </c>
       <c r="M8" t="n">
-        <v>8.612630703414004</v>
+        <v>8.589767536107662</v>
       </c>
       <c r="N8" t="n">
-        <v>126.2698325347153</v>
+        <v>125.6820127303626</v>
       </c>
       <c r="O8" t="n">
-        <v>11.23698502867719</v>
+        <v>11.2107989336337</v>
       </c>
       <c r="P8" t="n">
-        <v>369.2987895539417</v>
+        <v>369.2567005223348</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27175,28 +27315,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3856404996928515</v>
+        <v>-0.379900292228966</v>
       </c>
       <c r="J9" t="n">
+        <v>372</v>
+      </c>
+      <c r="K9" t="n">
         <v>370</v>
       </c>
-      <c r="K9" t="n">
-        <v>368</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09647161818095751</v>
+        <v>0.09459330401067612</v>
       </c>
       <c r="M9" t="n">
-        <v>7.178769253888852</v>
+        <v>7.172589688518142</v>
       </c>
       <c r="N9" t="n">
-        <v>82.03522367437513</v>
+        <v>81.77916547360628</v>
       </c>
       <c r="O9" t="n">
-        <v>9.057329831378294</v>
+        <v>9.043183370561845</v>
       </c>
       <c r="P9" t="n">
-        <v>375.8522314232977</v>
+        <v>375.790858568993</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27253,28 +27393,28 @@
         <v>0.0713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05063062969947663</v>
+        <v>0.05316735350671076</v>
       </c>
       <c r="J10" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K10" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0007819322996133193</v>
+        <v>0.0008710809265974895</v>
       </c>
       <c r="M10" t="n">
-        <v>10.67288128697937</v>
+        <v>10.63099648615573</v>
       </c>
       <c r="N10" t="n">
-        <v>194.6644246731086</v>
+        <v>193.6596634289099</v>
       </c>
       <c r="O10" t="n">
-        <v>13.95221934579257</v>
+        <v>13.91616554331364</v>
       </c>
       <c r="P10" t="n">
-        <v>358.5320216086637</v>
+        <v>358.5050679577004</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27331,28 +27471,28 @@
         <v>0.0857</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07364674993402678</v>
+        <v>-0.06658123907745341</v>
       </c>
       <c r="J11" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K11" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004764276003172974</v>
+        <v>0.0003933971010832149</v>
       </c>
       <c r="M11" t="n">
-        <v>17.15301159665058</v>
+        <v>17.08829505142693</v>
       </c>
       <c r="N11" t="n">
-        <v>660.5720754444778</v>
+        <v>657.2347139503055</v>
       </c>
       <c r="O11" t="n">
-        <v>25.70159674892745</v>
+        <v>25.63658935877207</v>
       </c>
       <c r="P11" t="n">
-        <v>361.8140656533428</v>
+        <v>361.7374734216108</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27409,28 +27549,28 @@
         <v>0.1315</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4148472870835317</v>
+        <v>-0.4031256063024439</v>
       </c>
       <c r="J12" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K12" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0530550153541528</v>
+        <v>0.05054810782621555</v>
       </c>
       <c r="M12" t="n">
-        <v>10.84523545399469</v>
+        <v>10.84145878195457</v>
       </c>
       <c r="N12" t="n">
-        <v>179.2461903269817</v>
+        <v>179.0300235696077</v>
       </c>
       <c r="O12" t="n">
-        <v>13.38828556339391</v>
+        <v>13.38021014669081</v>
       </c>
       <c r="P12" t="n">
-        <v>371.8847969925396</v>
+        <v>371.7582745122489</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27487,28 +27627,28 @@
         <v>0.1109</v>
       </c>
       <c r="I13" t="n">
-        <v>0.004912959907902844</v>
+        <v>0.01410509615122736</v>
       </c>
       <c r="J13" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K13" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L13" t="n">
-        <v>1.324873070551735e-05</v>
+        <v>0.0001098654980596914</v>
       </c>
       <c r="M13" t="n">
-        <v>8.065426208999739</v>
+        <v>8.070996314064912</v>
       </c>
       <c r="N13" t="n">
-        <v>108.3986189174327</v>
+        <v>108.288221227402</v>
       </c>
       <c r="O13" t="n">
-        <v>10.41146574298896</v>
+        <v>10.40616265620531</v>
       </c>
       <c r="P13" t="n">
-        <v>371.6383263597832</v>
+        <v>371.5407526952428</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27565,28 +27705,28 @@
         <v>0.0969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.311713189522409</v>
+        <v>-0.2933290849157767</v>
       </c>
       <c r="J14" t="n">
+        <v>372</v>
+      </c>
+      <c r="K14" t="n">
         <v>370</v>
       </c>
-      <c r="K14" t="n">
-        <v>368</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.03822262503661644</v>
+        <v>0.03390955361785586</v>
       </c>
       <c r="M14" t="n">
-        <v>9.529103037471382</v>
+        <v>9.581378896028422</v>
       </c>
       <c r="N14" t="n">
-        <v>145.4289343840381</v>
+        <v>146.5633417322157</v>
       </c>
       <c r="O14" t="n">
-        <v>12.05939195747605</v>
+        <v>12.10633477697588</v>
       </c>
       <c r="P14" t="n">
-        <v>373.2609546365805</v>
+        <v>373.0659444329151</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27643,28 +27783,28 @@
         <v>0.0607</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2301579785850346</v>
+        <v>-0.2104564479377788</v>
       </c>
       <c r="J15" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K15" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01737509715357777</v>
+        <v>0.01454153987869722</v>
       </c>
       <c r="M15" t="n">
-        <v>9.871354237158238</v>
+        <v>9.925884863794446</v>
       </c>
       <c r="N15" t="n">
-        <v>175.6020122620515</v>
+        <v>176.8403609969748</v>
       </c>
       <c r="O15" t="n">
-        <v>13.25149094487302</v>
+        <v>13.2981337411298</v>
       </c>
       <c r="P15" t="n">
-        <v>378.3873481271893</v>
+        <v>378.1755681223383</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27721,28 +27861,28 @@
         <v>0.0541</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4219643604681804</v>
+        <v>-0.40622032704833</v>
       </c>
       <c r="J16" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K16" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06322617281108833</v>
+        <v>0.05894877434232537</v>
       </c>
       <c r="M16" t="n">
-        <v>10.23032037604099</v>
+        <v>10.25709645647706</v>
       </c>
       <c r="N16" t="n">
-        <v>154.8625555951456</v>
+        <v>155.4194287358219</v>
       </c>
       <c r="O16" t="n">
-        <v>12.44437847363803</v>
+        <v>12.46673288138564</v>
       </c>
       <c r="P16" t="n">
-        <v>386.1785609817075</v>
+        <v>386.009175765911</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27799,28 +27939,28 @@
         <v>0.048</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7427824730225721</v>
+        <v>-0.7278416037134913</v>
       </c>
       <c r="J17" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K17" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02646598699876468</v>
+        <v>0.02567599391390074</v>
       </c>
       <c r="M17" t="n">
-        <v>21.70990547892395</v>
+        <v>21.66002447968877</v>
       </c>
       <c r="N17" t="n">
-        <v>1190.986523767648</v>
+        <v>1185.688105705384</v>
       </c>
       <c r="O17" t="n">
-        <v>34.5106726067118</v>
+        <v>34.43382211874516</v>
       </c>
       <c r="P17" t="n">
-        <v>371.4182032991179</v>
+        <v>371.2574949494413</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27858,7 +27998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R371"/>
+  <dimension ref="A1:R373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61701,6 +61841,190 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-37.775738969427316,174.83336085601033</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-37.775026583707415,174.83329560794527</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-37.77430484911077,174.83328958607274</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-37.77357842487379,174.83326100316208</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-37.77285650644353,174.83325663511857</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-37.77212869161271,174.8334224944588</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-37.77144083390976,174.83316752747302</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-37.770744942705896,174.83300057237935</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-37.77002901708353,174.8329633891326</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-37.769329037805186,174.8328020631584</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-37.768629349525796,174.83263562574533</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-37.76793797442101,174.83243607190508</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>-37.76724240887529,174.83228697264732</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-37.76655255069062,174.83206521438146</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>-37.76585266701156,174.83193215988007</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>-37.76511626345028,174.83203878758863</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-37.77574809565626,174.8332979885232</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-37.77502839922616,174.8332831015672</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-37.774309828498794,174.8332548447014</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-37.77358720345484,174.83318231676722</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-37.77286129986578,174.83319814635874</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-37.77213070935875,174.8334007346577</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-37.771444170308285,174.8331396923635</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-37.77074738205899,174.83298267270587</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-37.77003244002838,174.83293545637355</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-37.76933187125503,174.83277459830222</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-37.76863113946502,174.8326172621118</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-37.76793888246808,174.83242820930056</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>-37.7672478538016,174.83224623039726</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-37.766560948615165,174.83200322981548</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>-37.76585938431835,174.8318851306086</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>-37.76512005425034,174.83201323824582</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
